--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-09T09:28:26+00:00</t>
+    <t>2023-10-16T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:03:47+00:00</t>
+    <t>2023-10-16T13:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:05:21+00:00</t>
+    <t>2023-10-16T13:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -36,7 +36,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-practitioner-qualification</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-practitioner-qualification</t>
   </si>
   <si>
     <t>Version</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:49:57+00:00</t>
+    <t>2023-10-23T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T09:15:45+00:00</t>
+    <t>2023-10-23T11:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:28:06+00:00</t>
+    <t>2023-11-06T10:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:15:36+00:00</t>
+    <t>2023-11-07T09:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T09:05:25+00:00</t>
+    <t>2023-11-08T15:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T10:12:39+00:00</t>
+    <t>2023-12-04T10:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T10:06:25+00:00</t>
+    <t>2023-12-04T12:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:30:51+00:00</t>
+    <t>2023-12-04T12:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:19:21+00:00</t>
+    <t>2023-12-11T10:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -7,19 +7,19 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE-R48-DiplomeE" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from TRE_R48-DiplomeE" r:id="rId4" sheetId="2"/>
     <sheet name="Include from TRE-R47-Commissi" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE-R49-DiplomeE" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from TRE-R50-DESCGrou" r:id="rId7" sheetId="5"/>
-    <sheet name="Include from TRE-R51-DESCGrou" r:id="rId8" sheetId="6"/>
-    <sheet name="Include from TRE-R53-DiplomeP" r:id="rId9" sheetId="7"/>
-    <sheet name="Include from TRE-R54-DiplomeU" r:id="rId10" sheetId="8"/>
-    <sheet name="Include from TRE-R55-Certific" r:id="rId11" sheetId="9"/>
-    <sheet name="Include from TRE-R56-Attestat" r:id="rId12" sheetId="10"/>
-    <sheet name="Include from TRE-R52-Capacite" r:id="rId13" sheetId="11"/>
-    <sheet name="Include from TRE-R58-AutreTyp" r:id="rId14" sheetId="12"/>
-    <sheet name="Include from TRE-R36-AutreDip" r:id="rId15" sheetId="13"/>
-    <sheet name="Include from TRE-R226-Dip2iem" r:id="rId16" sheetId="14"/>
+    <sheet name="Include from TRE_R49-DiplomeE" r:id="rId6" sheetId="4"/>
+    <sheet name="Include from TRE_R50-DESCGrou" r:id="rId7" sheetId="5"/>
+    <sheet name="Include from TRE_R51-DESCGrou" r:id="rId8" sheetId="6"/>
+    <sheet name="Include from TRE_R53-DiplomeP" r:id="rId9" sheetId="7"/>
+    <sheet name="Include from TRE_R54-DiplomeU" r:id="rId10" sheetId="8"/>
+    <sheet name="Include from TRE_R55-Certific" r:id="rId11" sheetId="9"/>
+    <sheet name="Include from TRE_R56-Attestat" r:id="rId12" sheetId="10"/>
+    <sheet name="Include from TRE_R52-Capacite" r:id="rId13" sheetId="11"/>
+    <sheet name="Include from TRE_R58-AutreTyp" r:id="rId14" sheetId="12"/>
+    <sheet name="Include from TRE_R36-AutreDip" r:id="rId15" sheetId="13"/>
+    <sheet name="Include from TRE_R226-Dip2iem" r:id="rId16" sheetId="14"/>
   </sheets>
 </workbook>
 </file>
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/main/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
